--- a/Resources/exportedData/AllInvoices_12_23_2025.xlsx
+++ b/Resources/exportedData/AllInvoices_12_23_2025.xlsx
@@ -183,17 +183,12 @@
   <numFmts count="1">
     <numFmt numFmtId="171" formatCode="M/d/yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color auto="1"/>
-      <name val="Arial bold"/>
     </font>
     <font>
       <sz val="9"/>
@@ -207,12 +202,13 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial bold"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -221,16 +217,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFD3D3D3"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -251,29 +252,31 @@
         <color theme="2"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="0"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0">
-      <alignment vertical="top"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="header" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -290,8 +293,8 @@
       <xdr:rowOff>209550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>400757</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>38807</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1562100</xdr:rowOff>
     </xdr:to>
@@ -317,7 +320,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5276849" y="209550"/>
+          <a:off x="3743324" y="209550"/>
           <a:ext cx="7153983" cy="1352550"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -619,140 +622,145 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{3C351DBD-FB69-D2E7-C2F5-A4223CF53C1E}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{765D822A-5204-5E85-F013-610A63BF38A9}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:V6682"/>
   <sheetFormatPr defaultColWidth="9.140625" customHeight="1" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.140625" customWidth="1"/>
-    <col min="2" max="2" width="13.8515625" customWidth="1"/>
-    <col min="3" max="3" width="13.00390625" customWidth="1"/>
-    <col min="4" max="5" width="22.8515625" customWidth="1"/>
-    <col min="6" max="6" width="24.421875" customWidth="1"/>
-    <col min="7" max="7" width="7.140625" customWidth="1"/>
-    <col min="8" max="8" width="20.8515625" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" customWidth="1"/>
-    <col min="10" max="10" width="8.57421875" customWidth="1"/>
-    <col min="11" max="11" width="7.57421875" customWidth="1"/>
-    <col min="12" max="12" width="7.00390625" customWidth="1"/>
-    <col min="13" max="13" width="7.421875" customWidth="1"/>
-    <col min="14" max="14" width="9.00390625" customWidth="1"/>
+    <col min="1" max="1" width="4.28125" customWidth="1"/>
+    <col min="2" max="2" width="7.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.28125" customWidth="1"/>
+    <col min="4" max="6" width="17.140625" customWidth="1"/>
+    <col min="7" max="7" width="44.28125" customWidth="1"/>
+    <col min="8" max="8" width="5.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.57421875" customWidth="1"/>
+    <col min="10" max="10" width="4.28125" customWidth="1"/>
+    <col min="11" max="11" width="12.8515625" customWidth="1"/>
+    <col min="12" max="13" width="11.421875" customWidth="1"/>
+    <col min="14" max="14" width="8.57421875" customWidth="1"/>
+    <col min="15" max="15" width="11.421875" customWidth="1"/>
+    <col min="16" max="16" width="18.57421875" customWidth="1"/>
+    <col min="17" max="18" width="8.57421875" customWidth="1"/>
+    <col min="19" max="19" width="21.421875" customWidth="1"/>
+    <col min="20" max="20" width="5.7109375" customWidth="1"/>
+    <col min="21" max="21" width="14.28125" customWidth="1"/>
+    <col min="22" max="22" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row customHeight="1" ht="141">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
     </row>
     <row customHeight="1" ht="27.75">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
     </row>
-    <row customHeight="1" ht="15">
-      <c r="A3" s="5" t="s">
+    <row customHeight="1" ht="22.5">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="Q3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="R3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="S3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="T3" s="5" t="s">
+      <c r="T3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="U3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="V3" s="5" t="s">
+      <c r="V3" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -763,16 +771,16 @@
       <c r="B4" s="0">
         <v>11111</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>45432</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>45446</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>45446</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>45982</v>
       </c>
       <c r="G4" s="0" t="s">
@@ -831,16 +839,16 @@
       <c r="B5" s="0">
         <v>6857</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>44754</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>44886</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>44938</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <v>44945</v>
       </c>
       <c r="G5" s="0" t="s">
@@ -899,16 +907,16 @@
       <c r="B6" s="0">
         <v>9245</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>45096</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>45198</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>45251</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>45356</v>
       </c>
       <c r="G6" s="0" t="s">
@@ -967,10 +975,10 @@
       <c r="B7" s="0">
         <v>11189</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>46009</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>46009</v>
       </c>
       <c r="G7" s="0" t="s">
@@ -1029,13 +1037,13 @@
       <c r="B8" s="0">
         <v>9518</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>45140</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>45159</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>45170</v>
       </c>
       <c r="G8" s="0" t="s">
@@ -1094,16 +1102,16 @@
       <c r="B9" s="0">
         <v>10130</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>45229</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>45309</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>45308</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>45315</v>
       </c>
       <c r="G9" s="0" t="s">
@@ -1162,16 +1170,16 @@
       <c r="B10" s="0">
         <v>11039</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>45418</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>45446</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>45446</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>45418</v>
       </c>
       <c r="G10" s="0" t="s">
@@ -1230,13 +1238,13 @@
       <c r="B11" s="0">
         <v>10916</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>45394</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>45399</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="5">
         <v>45446</v>
       </c>
       <c r="G11" s="0" t="s">
@@ -1295,13 +1303,13 @@
       <c r="B12" s="0">
         <v>9000</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>45061</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="5">
         <v>45294</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <v>45303</v>
       </c>
       <c r="G12" s="0" t="s">
@@ -1360,13 +1368,13 @@
       <c r="B13" s="0">
         <v>10701</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>45342</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>45406</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="5">
         <v>45422</v>
       </c>
       <c r="G13" s="0" t="s">
@@ -1418,9 +1426,39 @@
         <v>0</v>
       </c>
     </row>
+    <row customHeight="1" ht="15">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6">
+        <v>7488.9575</v>
+      </c>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6">
+        <v>650</v>
+      </c>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6">
+        <v>0</v>
+      </c>
+      <c r="V14" s="6"/>
+    </row>
     <row r="6682" customHeight="1" ht="15.75">
-      <c r="B6682" s="2"/>
-      <c r="L6682" s="3"/>
+      <c r="B6682" s="1"/>
+      <c r="L6682" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
